--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
@@ -2429,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V4" t="n">
         <v>15</v>
@@ -2604,13 +2604,13 @@
         <v>89</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="CA4" t="n">
         <v>1.85</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="CC4" t="n">
         <v>1</v>
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="CR4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CS4" t="n">
         <v>33</v>
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V5" t="n">
         <v>5</v>
@@ -3052,13 +3052,13 @@
         <v>88</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="CA5" t="n">
         <v>0.77</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY6" t="n">
         <v>6</v>
@@ -3802,13 +3802,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U7" t="n">
         <v>12</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W7" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
         <v>1.59</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS7" t="n">
         <v>23</v>
@@ -4046,7 +4046,7 @@
         <v>7</v>
       </c>
       <c r="CV7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL8" headerRowCount="1">
-  <autoFilter ref="A1:EL8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL14" headerRowCount="1">
+  <autoFilter ref="A1:EL14"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,14 +580,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL8"/>
+  <dimension ref="A1:EL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="16.8" customWidth="1" min="5" max="5"/>
     <col width="25.2" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -609,8 +609,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
-    <col width="39.6" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4636,6 +4636,2734 @@
       <c r="EL8" t="inlineStr">
         <is>
           <t>2.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aalesund</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46102.625</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Sparebanken Sør Arena</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Stadionveien 21, Kristiansand</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>133</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46102.70833333334</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>20</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>335</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>64</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46103.5625</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>13</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9</v>
+      </c>
+      <c r="X11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Lerkendal Stadion</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Klæbuveien 125, Trondheim</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>327</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="inlineStr"/>
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr"/>
+      <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46103.66666666666</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Komplett Arena</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Nygårdsveien 84, Sandefjord</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>340</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP12" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ12" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>46103.66666666666</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>14</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Nye Fredrikstad Stadion</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>K.G. Mehldalsvei 7, Kråkerøy, Fredrikstad</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1471</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>46103.66666666666</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" t="n">
+        <v>12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Brann Stadion</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Kniksens plass 1, Bergen</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>331</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>130</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>37</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW14" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>2.52</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -6016,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6068,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>2.06</v>
@@ -6188,13 +6188,13 @@
         <v>1</v>
       </c>
       <c r="BR12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU12" t="n">
         <v>1</v>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -1759,7 +1759,7 @@
         <v>14</v>
       </c>
       <c r="CY2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
         <v>13</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
         <v>13</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>1.93</v>
@@ -2124,13 +2124,13 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS3" t="n">
         <v>3</v>
       </c>
       <c r="BT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU3" t="n">
         <v>1</v>
@@ -2151,10 +2151,10 @@
         <v>1.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -5169,10 +5169,10 @@
         <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
@@ -5390,7 +5390,7 @@
         <v>15</v>
       </c>
       <c r="CV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5583,13 +5583,13 @@
         <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
         <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V11" t="n">
         <v>10</v>
@@ -5764,13 +5764,13 @@
         <v>55</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="CA11" t="n">
         <v>1.24</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
@@ -6962,13 +6962,13 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
         <v>10</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>12</v>
@@ -7143,10 +7143,10 @@
         <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>1</v>
       </c>
       <c r="CU14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV14" t="n">
         <v>12</v>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL14" headerRowCount="1">
-  <autoFilter ref="A1:EL14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL22" headerRowCount="1">
+  <autoFilter ref="A1:EL22"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,14 +580,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL14"/>
+  <dimension ref="A1:EL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
-    <col width="16.8" customWidth="1" min="5" max="5"/>
+    <col width="20.4" customWidth="1" min="5" max="5"/>
     <col width="25.2" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2694,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2823,164 +2823,164 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
         <v>46096.66666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>KFUM Arena</t>
+          <t>Intility Arena</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Ekebergveien 101, Oslo</t>
+          <t>Innspurten 1, Oslo</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.63</v>
+        <v>3.46</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.11</v>
+        <v>2.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.69</v>
+        <v>3.75</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1524</v>
+        <v>327</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
@@ -3001,64 +3001,64 @@
         <v>1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BK5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BN5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU5" t="n">
         <v>1</v>
       </c>
       <c r="BV5" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="BW5" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BX5" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="BY5" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.77</v>
+        <v>1.82</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.54</v>
+        <v>3.41</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -3097,37 +3097,37 @@
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ5" t="n">
         <v>1</v>
       </c>
       <c r="CR5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CS5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="CT5" t="n">
         <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CW5" t="n">
         <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CY5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3175,13 +3175,13 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
       </c>
       <c r="DQ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="b">
         <v>0</v>
@@ -3200,84 +3200,68 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3647,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3751,40 +3735,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>46096.66666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3793,122 +3777,122 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" t="n">
-        <v>4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>13</v>
-      </c>
-      <c r="U7" t="n">
-        <v>12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>17</v>
-      </c>
       <c r="W7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Intility Arena</t>
+          <t>KFUM Arena</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Innspurten 1, Oslo</t>
+          <t>Ekebergveien 101, Oslo</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.46</v>
+        <v>2.63</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.05</v>
+        <v>3.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.75</v>
+        <v>2.69</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>327</v>
+        <v>1524</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -3929,133 +3913,133 @@
         <v>1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX7" t="n">
         <v>6</v>
       </c>
-      <c r="BK7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>67</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>108</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>11</v>
-      </c>
       <c r="CY7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -4070,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4103,13 +4087,13 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
       </c>
       <c r="DQ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR7" t="b">
         <v>0</v>
@@ -4128,68 +4112,84 @@
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr"/>
-      <c r="DY7" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EK7" t="inlineStr"/>
-      <c r="EL7" t="inlineStr"/>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4521,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -5983,31 +5983,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>46103.66666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
         <v>9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -6016,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6025,122 +6025,122 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>6</v>
       </c>
       <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
         <v>10</v>
       </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>16</v>
-      </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Komplett Arena</t>
+          <t>Brann Stadion</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Nygårdsveien 84, Sandefjord</t>
+          <t>Kniksens plass 1, Bergen</t>
         </is>
       </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.15</v>
+        <v>3.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA12" t="n">
         <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
@@ -6161,76 +6161,76 @@
         <v>1</v>
       </c>
       <c r="BI12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BK12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BL12" t="n">
         <v>2</v>
       </c>
       <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5</v>
       </c>
-      <c r="BN12" t="n">
-        <v>10</v>
-      </c>
       <c r="BO12" t="n">
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ12" t="n">
         <v>1</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU12" t="n">
         <v>1</v>
       </c>
       <c r="BV12" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="BW12" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="BX12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="BY12" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.12</v>
+        <v>2.77</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE12" t="n">
         <v>0</v>
       </c>
       <c r="CF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>0</v>
@@ -6248,13 +6248,13 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
@@ -6266,19 +6266,19 @@
         <v>1</v>
       </c>
       <c r="CR12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="CS12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT12" t="n">
         <v>1</v>
       </c>
       <c r="CU12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CV12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CW12" t="n">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>7</v>
       </c>
       <c r="CY12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CZ12" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="DR12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS12" t="b">
         <v>0</v>
@@ -6356,72 +6356,88 @@
         <v>0</v>
       </c>
       <c r="DV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW12" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
       <c r="DZ12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EA12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EB12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EC12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="ED12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EE12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EF12" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH12" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr">
+        <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="EI12" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EJ12" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EK12" t="inlineStr"/>
-      <c r="EL12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6791,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6911,31 +6927,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>46103.66666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="n">
         <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>15</v>
@@ -6944,7 +6960,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -6953,122 +6969,122 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
         <v>6</v>
       </c>
       <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>18</v>
+      </c>
+      <c r="X14" t="n">
         <v>7</v>
       </c>
-      <c r="T14" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10</v>
-      </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>13</v>
-      </c>
       <c r="Y14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Brann Stadion</t>
+          <t>Komplett Arena</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Kniksens plass 1, Bergen</t>
+          <t>Nygårdsveien 84, Sandefjord</t>
         </is>
       </c>
       <c r="AC14" t="n">
         <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7089,124 +7105,124 @@
         <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU14" t="n">
         <v>7</v>
       </c>
-      <c r="BK14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>54</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>39</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>130</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>37</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>12</v>
-      </c>
       <c r="CV14" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW14" t="n">
         <v>1</v>
@@ -7215,157 +7231,3701 @@
         <v>7</v>
       </c>
       <c r="CY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr"/>
+      <c r="DY14" t="inlineStr"/>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46118.52083333334</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Intility Arena</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Innspurten 1, Oslo</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>335</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>14712</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP15" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="inlineStr"/>
+      <c r="DX15" t="inlineStr"/>
+      <c r="DY15" t="inlineStr"/>
+      <c r="DZ15" t="inlineStr"/>
+      <c r="EA15" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr"/>
+      <c r="EH15" t="inlineStr"/>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>46118.625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>14</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Kristiansund Stadion</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Hærnøsandveien 19, Kristiansund</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>332</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3737</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>83</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>141</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="inlineStr"/>
+      <c r="DX16" t="inlineStr"/>
+      <c r="DY16" t="inlineStr"/>
+      <c r="DZ16" t="inlineStr"/>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>11.08</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr"/>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46118.625</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16</v>
+      </c>
+      <c r="W17" t="n">
+        <v>22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Aker Stadion</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Julsundveien 14, Reknes, Molde</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>339</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5749</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>139</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>22</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY17" t="n">
         <v>13</v>
       </c>
-      <c r="CZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>3</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DR14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DS14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW14" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="DX14" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="DY14" t="inlineStr">
+      <c r="CZ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP17" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr"/>
+      <c r="DY17" t="inlineStr"/>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46118.625</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>17</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Sarpsborg Stadion</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Haftor Joenssonsgata 19, Sarpsborg</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5422</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr"/>
+      <c r="DY18" t="inlineStr"/>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr"/>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr"/>
+      <c r="EL18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46118.625</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>13</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
+        <v>11</v>
+      </c>
+      <c r="U19" t="n">
+        <v>15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>20</v>
+      </c>
+      <c r="W19" t="n">
+        <v>11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Briskeby Arena</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Arenavegen 2, Briskebyen, Hamar</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>336</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5165</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>100</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ19" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr"/>
+      <c r="EL19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46118.71875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>17</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>331</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6027</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP20" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ20" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr"/>
+      <c r="EH20" t="inlineStr"/>
+      <c r="EI20" t="inlineStr"/>
+      <c r="EJ20" t="inlineStr"/>
+      <c r="EK20" t="inlineStr"/>
+      <c r="EL20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Aalesund</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46119.70833333334</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Color Line Stadion</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Sjømannsveien 14, Ålesund</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1471</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW21" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="ED21" t="inlineStr"/>
+      <c r="EE21" t="inlineStr"/>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr"/>
+      <c r="EL21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46119.70833333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>9</v>
+      </c>
+      <c r="V22" t="n">
+        <v>13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>7</v>
+      </c>
+      <c r="X22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>KFUM Arena</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Ekebergveien 101, Oslo</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>342</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX22" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW22" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EF22" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="DZ14" t="inlineStr">
-        <is>
-          <t>2.96</t>
-        </is>
-      </c>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EC14" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EK14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EL14" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EJ22" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr"/>
+      <c r="EL22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -7860,7 +7860,7 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -7872,7 +7872,7 @@
         <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
         <v>9</v>
@@ -8047,10 +8047,10 @@
         <v>0.76</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CS16" t="n">
         <v>27</v>
@@ -8116,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CY16" t="n">
         <v>5</v>
@@ -10106,13 +10106,13 @@
         <v>18</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-1</v>
+        <v>4008</v>
       </c>
       <c r="BG21" t="n">
         <v>2</v>
@@ -10335,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="CU21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV21" t="n">
         <v>18</v>
@@ -10344,10 +10344,10 @@
         <v>1</v>
       </c>
       <c r="CX21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CY21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ21" t="n">
         <v>100</v>
@@ -10418,29 +10418,13 @@
       <c r="DV21" t="b">
         <v>1</v>
       </c>
-      <c r="DW21" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="DX21" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="DY21" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="DZ21" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
+      <c r="DW21" t="inlineStr"/>
+      <c r="DX21" t="inlineStr"/>
+      <c r="DY21" t="inlineStr"/>
+      <c r="DZ21" t="inlineStr"/>
       <c r="EA21" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="EB21" t="inlineStr">
@@ -10450,7 +10434,7 @@
       </c>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr"/>
@@ -10460,12 +10444,12 @@
       <c r="EH21" t="inlineStr"/>
       <c r="EI21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EJ21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK21" t="inlineStr"/>
@@ -10532,19 +10516,19 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
         <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W22" t="n">
         <v>7</v>
@@ -10553,10 +10537,10 @@
         <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -10656,7 +10640,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-1</v>
+        <v>1365</v>
       </c>
       <c r="BG22" t="n">
         <v>2</v>
@@ -10716,13 +10700,13 @@
         <v>98</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -10864,64 +10848,64 @@
       </c>
       <c r="DW22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DX22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EA22" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EB22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EG22" t="inlineStr"/>
       <c r="EH22" t="inlineStr"/>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr"/>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL22" headerRowCount="1">
-  <autoFilter ref="A1:EL22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL25" headerRowCount="1">
+  <autoFilter ref="A1:EL25"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL22"/>
+  <dimension ref="A1:EL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4057,7 +4057,7 @@
         <v>1.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -5983,31 +5983,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>46103.66666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -6016,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6025,122 +6025,122 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
         <v>6</v>
       </c>
       <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18</v>
+      </c>
+      <c r="X12" t="n">
         <v>7</v>
       </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V12" t="n">
-        <v>13</v>
-      </c>
-      <c r="W12" t="n">
-        <v>12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13</v>
-      </c>
       <c r="Y12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Brann Stadion</t>
+          <t>Komplett Arena</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Kniksens plass 1, Bergen</t>
+          <t>Nygårdsveien 84, Sandefjord</t>
         </is>
       </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
@@ -6161,124 +6161,124 @@
         <v>1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
         <v>7</v>
       </c>
-      <c r="BK12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>54</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>39</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>130</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>37</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>12</v>
-      </c>
       <c r="CV12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW12" t="n">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>7</v>
       </c>
       <c r="CY12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CZ12" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="DR12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS12" t="b">
         <v>0</v>
@@ -6356,88 +6356,72 @@
         <v>0</v>
       </c>
       <c r="DV12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="inlineStr">
         <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="DX12" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="DY12" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
       <c r="DZ12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EA12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EB12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EC12" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="ED12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EF12" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EG12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EH12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EJ12" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EK12" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EL12" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6455,40 +6439,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
         <v>46103.66666666666</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -6497,104 +6481,104 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V13" t="n">
         <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Nye Fredrikstad Stadion</t>
+          <t>Brann Stadion</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>K.G. Mehldalsvei 7, Kråkerøy, Fredrikstad</t>
+          <t>Kniksens plass 1, Bergen</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW13" t="n">
         <v>1</v>
@@ -6603,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB13" t="n">
-        <v>1471</v>
+        <v>331</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
@@ -6633,22 +6617,22 @@
         <v>1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BK13" t="n">
         <v>3</v>
       </c>
       <c r="BL13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -6657,40 +6641,40 @@
         <v>1</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS13" t="n">
         <v>1</v>
       </c>
       <c r="BT13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU13" t="n">
         <v>1</v>
       </c>
       <c r="BV13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BW13" t="n">
         <v>39</v>
       </c>
       <c r="BX13" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="BY13" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -6717,16 +6701,16 @@
         <v>1</v>
       </c>
       <c r="CK13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
@@ -6738,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="CR13" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="CS13" t="n">
         <v>24</v>
@@ -6747,19 +6731,19 @@
         <v>1</v>
       </c>
       <c r="CU13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV13" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX13" t="n">
         <v>7</v>
       </c>
-      <c r="CW13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>5</v>
-      </c>
       <c r="CY13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ13" t="n">
         <v>0</v>
@@ -6774,10 +6758,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6819,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="DS13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="b">
         <v>0</v>
@@ -6832,82 +6816,82 @@
       </c>
       <c r="DW13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="DZ13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EA13" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EB13" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EC13" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="ED13" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EE13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EF13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH13" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="EI13" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
       <c r="EJ13" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.52</t>
         </is>
       </c>
     </row>
@@ -6927,40 +6911,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>46103.66666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -6969,107 +6953,107 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="Z14" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Komplett Arena</t>
+          <t>Nye Fredrikstad Stadion</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Nygårdsveien 84, Sandefjord</t>
+          <t>K.G. Mehldalsvei 7, Kråkerøy, Fredrikstad</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="AK14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>1.45</v>
       </c>
-      <c r="AL14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AR14" t="n">
-        <v>2.22</v>
+        <v>2.94</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
@@ -7081,10 +7065,10 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>340</v>
+        <v>1471</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7105,37 +7089,37 @@
         <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL14" t="n">
         <v>4</v>
       </c>
-      <c r="BK14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>2</v>
-      </c>
       <c r="BM14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT14" t="n">
         <v>1</v>
@@ -7144,37 +7128,37 @@
         <v>1</v>
       </c>
       <c r="BV14" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="BW14" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="BX14" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="BY14" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
@@ -7189,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -7213,25 +7197,25 @@
         <v>21</v>
       </c>
       <c r="CS14" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
       </c>
       <c r="CU14" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV14" t="n">
         <v>7</v>
       </c>
-      <c r="CV14" t="n">
-        <v>17</v>
-      </c>
       <c r="CW14" t="n">
         <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CZ14" t="n">
         <v>0</v>
@@ -7246,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DE14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7261,7 +7245,7 @@
         <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -7279,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7288,10 +7272,10 @@
         <v>1</v>
       </c>
       <c r="DR14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT14" t="b">
         <v>0</v>
@@ -7300,72 +7284,88 @@
         <v>0</v>
       </c>
       <c r="DV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="DX14" t="inlineStr"/>
-      <c r="DY14" t="inlineStr"/>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EC14" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="ED14" t="inlineStr">
         <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EK14" t="inlineStr"/>
-      <c r="EL14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7830,25 +7830,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -7860,104 +7860,104 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
         <v>9</v>
       </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="Z16" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Kristiansund Stadion</t>
+          <t>Aker Stadion</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Hærnøsandveien 19, Kristiansund</t>
+          <t>Julsundveien 14, Reknes, Molde</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>2.87</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -7969,10 +7969,10 @@
         <v>1</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>3737</v>
+        <v>5749</v>
       </c>
       <c r="BG16" t="n">
         <v>2</v>
@@ -7993,64 +7993,64 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BO16" t="n">
         <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="BW16" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="BX16" t="n">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="BY16" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.76</v>
+        <v>1.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8086,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8098,40 +8098,40 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CS16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="CV16" t="n">
+        <v>22</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX16" t="n">
         <v>9</v>
       </c>
-      <c r="CW16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>10</v>
-      </c>
       <c r="CY16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CZ16" t="n">
         <v>50</v>
       </c>
       <c r="DA16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB16" t="n">
         <v>50</v>
       </c>
       <c r="DC16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD16" t="n">
         <v>1.5</v>
@@ -8143,40 +8143,40 @@
         <v>3</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.77</v>
+        <v>3.47</v>
       </c>
       <c r="DO16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
         <v>0</v>
@@ -8190,46 +8190,58 @@
       <c r="DV16" t="b">
         <v>0</v>
       </c>
-      <c r="DW16" t="inlineStr"/>
+      <c r="DW16" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
       <c r="DX16" t="inlineStr"/>
       <c r="DY16" t="inlineStr"/>
-      <c r="DZ16" t="inlineStr"/>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr"/>
@@ -8251,176 +8263,176 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>46118.625</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="K17" t="n">
+      <c r="U17" t="n">
+        <v>17</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sarpsborg Stadion</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Haftor Joenssonsgata 19, Sarpsborg</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>16</v>
-      </c>
-      <c r="W17" t="n">
-        <v>22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Aker Stadion</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Julsundveien 14, Reknes, Molde</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.87</v>
+        <v>4.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="AP17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR17" t="n">
         <v>2.2</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AS17" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>339</v>
+        <v>-1</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>5749</v>
+        <v>5422</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -8432,61 +8444,61 @@
         <v>5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="BW17" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX17" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="BY17" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.56</v>
+        <v>0.84</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.06</v>
+        <v>2.66</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8519,10 +8531,10 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8534,19 +8546,19 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="CS17" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
         <v>15</v>
       </c>
-      <c r="CT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>14</v>
-      </c>
       <c r="CV17" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
@@ -8555,37 +8567,37 @@
         <v>9</v>
       </c>
       <c r="CY17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
         <v>50</v>
       </c>
-      <c r="DA17" t="n">
-        <v>100</v>
-      </c>
       <c r="DB17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DE17" t="n">
-        <v>3</v>
+        <v>0.33</v>
       </c>
       <c r="DF17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DI17" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DJ17" t="n">
         <v>50</v>
@@ -8594,13 +8606,13 @@
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.97</v>
+        <v>0.77</v>
       </c>
       <c r="DN17" t="n">
-        <v>3.47</v>
+        <v>0.77</v>
       </c>
       <c r="DO17" t="n">
         <v>2</v>
@@ -8609,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="b">
         <v>0</v>
@@ -8624,60 +8636,60 @@
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr"/>
       <c r="DY17" t="inlineStr"/>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr"/>
@@ -8699,12 +8711,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -8714,25 +8726,25 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -8744,287 +8756,287 @@
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
+        <v>11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>15</v>
+      </c>
+      <c r="V18" t="n">
+        <v>20</v>
+      </c>
+      <c r="W18" t="n">
+        <v>11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Briskeby Arena</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Arenavegen 2, Briskebyen, Hamar</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU18" t="n">
         <v>6</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>336</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5165</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS18" t="n">
         <v>17</v>
       </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY18" t="n">
         <v>8</v>
       </c>
-      <c r="X18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Sarpsborg Stadion</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Haftor Joenssonsgata 19, Sarpsborg</t>
-        </is>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5422</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>74</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="DF18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
@@ -9033,22 +9045,22 @@
         <v>3</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.77</v>
+        <v>1.85</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.77</v>
+        <v>3.1</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
@@ -9060,72 +9072,80 @@
         <v>1</v>
       </c>
       <c r="DR18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV18" t="b">
         <v>1</v>
       </c>
       <c r="DW18" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="DX18" t="inlineStr"/>
-      <c r="DY18" t="inlineStr"/>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
       <c r="DZ18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EA18" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EB18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EC18" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="ED18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EE18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EF18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EG18" t="inlineStr"/>
       <c r="EH18" t="inlineStr"/>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr"/>
@@ -9147,40 +9167,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>46118.625</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -9189,101 +9209,101 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>9</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="U19" t="n">
+        <v>6</v>
+      </c>
+      <c r="V19" t="n">
         <v>15</v>
       </c>
-      <c r="V19" t="n">
-        <v>20</v>
-      </c>
       <c r="W19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Briskeby Arena</t>
+          <t>Kristiansund Stadion</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Arenavegen 2, Briskebyen, Hamar</t>
+          <t>Hærnøsandveien 19, Kristiansund</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.68</v>
+        <v>8.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AO19" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -9292,31 +9312,31 @@
         <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>5165</v>
+        <v>3737</v>
       </c>
       <c r="BG19" t="n">
         <v>2</v>
@@ -9325,124 +9345,124 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
         <v>5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
         <v>1</v>
       </c>
       <c r="BM19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>83</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>141</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV19" t="n">
         <v>9</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>43</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>95</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>11</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
@@ -9451,19 +9471,19 @@
         <v>10</v>
       </c>
       <c r="CY19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CZ19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DC19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD19" t="n">
         <v>1.5</v>
@@ -9490,13 +9510,13 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>3.1</v>
+        <v>1.77</v>
       </c>
       <c r="DO19" t="n">
         <v>2</v>
@@ -9511,77 +9531,57 @@
         <v>1</v>
       </c>
       <c r="DS19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW19" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="DX19" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="DZ19" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW19" t="inlineStr"/>
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr"/>
+      <c r="DZ19" t="inlineStr"/>
       <c r="EA19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EB19" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="EC19" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="ED19" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EE19" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr"/>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr"/>
@@ -10094,13 +10094,13 @@
         <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>15</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
         <v>18</v>
@@ -10109,10 +10109,10 @@
         <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         <v>1.71</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -10910,6 +10910,1310 @@
       </c>
       <c r="EK22" t="inlineStr"/>
       <c r="EL22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46123.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Åråsen Stadion</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>C.J. Hansensvej 3b, Kjeller</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>339</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW23" t="inlineStr"/>
+      <c r="DX23" t="inlineStr"/>
+      <c r="DY23" t="inlineStr"/>
+      <c r="DZ23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr"/>
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr"/>
+      <c r="EL23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46123.58333333334</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>16</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>331</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX24" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP24" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ24" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW24" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr"/>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EA24" t="inlineStr">
+        <is>
+          <t>10.96</t>
+        </is>
+      </c>
+      <c r="EB24" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC24" t="inlineStr">
+        <is>
+          <t>6.30</t>
+        </is>
+      </c>
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE24" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EF24" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
+      <c r="EK24" t="inlineStr"/>
+      <c r="EL24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46123.66666666666</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>335</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>58</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY25" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>100</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DN25" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="DO25" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW25" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EA25" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EB25" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EC25" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE25" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EF25" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr"/>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
+      <c r="EK25" t="inlineStr"/>
+      <c r="EL25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Norway_Eliteserien_2026.xlsx
+++ b/data/matches/leagues/Norway_Eliteserien_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL89" headerRowCount="1">
-  <autoFilter ref="A1:EL89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL90" headerRowCount="1">
+  <autoFilter ref="A1:EL90"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL89"/>
+  <dimension ref="A1:EL90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE3" t="n">
         <v>0.2</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>1.67</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3235,76 +3235,76 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
         <v>46096.66666666666</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7</v>
-      </c>
-      <c r="S6" t="n">
-        <v>7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
+        <v>9</v>
+      </c>
+      <c r="X6" t="n">
         <v>11</v>
       </c>
-      <c r="X6" t="n">
-        <v>9</v>
-      </c>
       <c r="Y6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z6" t="n">
         <v>40</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>60</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -3312,79 +3312,79 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.07</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.41</v>
+        <v>3.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>339</v>
+        <v>1524</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -3405,64 +3405,64 @@
         <v>1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4</v>
       </c>
-      <c r="BK6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL6" t="n">
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
         <v>3</v>
       </c>
-      <c r="BM6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
       <c r="BT6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="BW6" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="BX6" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="BY6" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.97</v>
+        <v>0.77</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.61</v>
+        <v>2.54</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="CK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
@@ -3498,41 +3498,41 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ6" t="n">
         <v>1</v>
       </c>
       <c r="CR6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="CT6" t="n">
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CV6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY6" t="n">
         <v>8</v>
       </c>
-      <c r="CY6" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ6" t="n">
         <v>0</v>
       </c>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.67</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3588,10 +3588,10 @@
         <v>1</v>
       </c>
       <c r="DR6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="b">
         <v>0</v>
@@ -3600,70 +3600,86 @@
         <v>0</v>
       </c>
       <c r="DV6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr"/>
-      <c r="EH6" t="inlineStr"/>
-      <c r="EI6" t="inlineStr"/>
-      <c r="EJ6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3683,40 +3699,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
         <v>46096.66666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3725,34 +3741,34 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" t="n">
+        <v>11</v>
+      </c>
+      <c r="X7" t="n">
         <v>9</v>
       </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>15</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>9</v>
-      </c>
-      <c r="X7" t="n">
-        <v>11</v>
-      </c>
       <c r="Y7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="n">
         <v>60</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
@@ -3760,79 +3776,79 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>3.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AJ7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AT7" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1524</v>
+        <v>339</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -3853,64 +3869,64 @@
         <v>1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK7" t="n">
         <v>2</v>
       </c>
       <c r="BL7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="BW7" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="BX7" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.77</v>
+        <v>1.97</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.54</v>
+        <v>3.61</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -3937,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
@@ -3946,41 +3962,41 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
         <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS7" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="CT7" t="n">
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CV7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>
       </c>
       <c r="CX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY7" t="n">
         <v>6</v>
       </c>
-      <c r="CY7" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ7" t="n">
         <v>0</v>
       </c>
@@ -3994,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE7" t="n">
         <v>1.67</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4036,10 +4052,10 @@
         <v>1</v>
       </c>
       <c r="DR7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT7" t="b">
         <v>0</v>
@@ -4048,86 +4064,70 @@
         <v>0</v>
       </c>
       <c r="DV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EJ7" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8446,7 +8446,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE17" t="n">
         <v>1.67</v>
@@ -8479,7 +8479,7 @@
         <v>3.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10637,7 +10637,7 @@
         <v>1.67</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF22" t="n">
         <v>3</v>
@@ -10667,7 +10667,7 @@
         <v>3.59</v>
       </c>
       <c r="DO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -13706,7 +13706,7 @@
         <v>25</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE29" t="n">
         <v>0.5</v>
@@ -14121,7 +14121,7 @@
         <v>1.2</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF30" t="n">
         <v>0</v>
@@ -14151,7 +14151,7 @@
         <v>2.91</v>
       </c>
       <c r="DO30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14235,38 +14235,38 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
         <v>46127.70833333334</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
         <v>6</v>
       </c>
-      <c r="K31" t="n">
-        <v>5</v>
-      </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -14281,34 +14281,34 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W31" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="X31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="Z31" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
@@ -14319,58 +14319,58 @@
         <v>2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="AF31" t="n">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.85</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.57</v>
+        <v>1.74</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="AO31" t="n">
-        <v>2.26</v>
+        <v>3.72</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.44</v>
+        <v>1.84</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW31" t="n">
         <v>0</v>
@@ -14379,13 +14379,13 @@
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB31" t="n">
         <v>-1</v>
@@ -14394,13 +14394,13 @@
         <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BE31" t="n">
         <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>5256</v>
+        <v>4549</v>
       </c>
       <c r="BG31" t="n">
         <v>2</v>
@@ -14412,184 +14412,184 @@
         <v>3</v>
       </c>
       <c r="BJ31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL31" t="n">
         <v>3</v>
       </c>
       <c r="BM31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>163</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>52</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>163</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV31" t="n">
         <v>6</v>
       </c>
-      <c r="BO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>72</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>160</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>73</v>
-      </c>
-      <c r="BZ31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CA31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CB31" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI31" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM31" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS31" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT31" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU31" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV31" t="n">
-        <v>19</v>
-      </c>
       <c r="CW31" t="n">
         <v>1</v>
       </c>
       <c r="CX31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CY31" t="n">
         <v>6</v>
       </c>
       <c r="CZ31" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA31" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB31" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DC31" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="DF31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG31" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DH31" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="DI31" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DJ31" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL31" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="DM31" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="DN31" t="n">
-        <v>3.77</v>
+        <v>3.42</v>
       </c>
       <c r="DO31" t="n">
         <v>11</v>
       </c>
       <c r="DP31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR31" t="b">
         <v>0</v>
@@ -14604,80 +14604,72 @@
         <v>0</v>
       </c>
       <c r="DV31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW31" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DX31" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="DY31" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="DZ31" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="EA31" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="EB31" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EC31" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="ED31" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EE31" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF31" t="inlineStr">
         <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EG31" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH31" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EI31" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EJ31" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EK31" t="inlineStr"/>
-      <c r="EL31" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG31" t="inlineStr"/>
+      <c r="EH31" t="inlineStr"/>
+      <c r="EI31" t="inlineStr"/>
+      <c r="EJ31" t="inlineStr"/>
+      <c r="EK31" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EL31" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14691,80 +14683,80 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
         <v>46127.70833333334</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="n">
         <v>4</v>
       </c>
-      <c r="K32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="U32" t="n">
+        <v>12</v>
+      </c>
+      <c r="V32" t="n">
         <v>10</v>
       </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="W32" t="n">
+        <v>19</v>
+      </c>
+      <c r="X32" t="n">
         <v>8</v>
       </c>
-      <c r="R32" t="n">
-        <v>4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>15</v>
-      </c>
-      <c r="V32" t="n">
-        <v>16</v>
-      </c>
-      <c r="W32" t="n">
-        <v>7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>7</v>
-      </c>
       <c r="Y32" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="Z32" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
@@ -14775,58 +14767,58 @@
         <v>2</v>
       </c>
       <c r="AE32" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>3.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.74</v>
+        <v>2.57</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="AO32" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="AU32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
@@ -14835,13 +14827,13 @@
         <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
         <v>-1</v>
@@ -14850,13 +14842,13 @@
         <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BE32" t="n">
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>4549</v>
+        <v>5256</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -14868,20 +14860,20 @@
         <v>3</v>
       </c>
       <c r="BJ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK32" t="n">
         <v>3</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>1</v>
       </c>
       <c r="BL32" t="n">
         <v>3</v>
       </c>
       <c r="BM32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN32" t="n">
         <v>6</v>
       </c>
-      <c r="BN32" t="n">
-        <v>4</v>
-      </c>
       <c r="BO32" t="n">
         <v>0</v>
       </c>
@@ -14904,37 +14896,37 @@
         <v>1</v>
       </c>
       <c r="BV32" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="BW32" t="n">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="BX32" t="n">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="BY32" t="n">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="CA32" t="n">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.23</v>
+        <v>3.01</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
       </c>
       <c r="CD32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE32" t="n">
         <v>0</v>
       </c>
       <c r="CF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG32" t="n">
         <v>0</v>
@@ -14955,10 +14947,10 @@
         <v>0</v>
       </c>
       <c r="CM32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO32" t="n">
         <v>0</v>
@@ -14970,82 +14962,82 @@
         <v>1</v>
       </c>
       <c r="CR32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS32" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CT32" t="n">
         <v>1</v>
       </c>
       <c r="CU32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV32" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CW32" t="n">
         <v>1</v>
       </c>
       <c r="CX32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CY32" t="n">
         <v>6</v>
       </c>
       <c r="CZ32" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA32" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="DC32" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="DF32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DG32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH32" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="DI32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DJ32" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL32" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="DM32" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="DN32" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="DO32" t="n">
         <v>11</v>
       </c>
       <c r="DP32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR32" t="b">
         <v>0</v>
@@ -15060,72 +15052,80 @@
         <v>0</v>
       </c>
       <c r="DV32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW32" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="DX32" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="DY32" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DZ32" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EA32" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB32" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="EC32" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="ED32" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EE32" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EF32" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG32" t="inlineStr"/>
-      <c r="EH32" t="inlineStr"/>
-      <c r="EI32" t="inlineStr"/>
-      <c r="EJ32" t="inlineStr"/>
-      <c r="EK32" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EL32" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG32" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH32" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EI32" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EJ32" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EK32" t="inlineStr"/>
+      <c r="EL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15915,7 +15915,7 @@
         <v>2.52</v>
       </c>
       <c r="DO34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -18555,7 +18555,7 @@
         <v>3.13</v>
       </c>
       <c r="DO40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19858,7 +19858,7 @@
         <v>59</v>
       </c>
       <c r="DD43" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE43" t="n">
         <v>0.8</v>
@@ -19891,7 +19891,7 @@
         <v>3.08</v>
       </c>
       <c r="DO43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -19979,135 +19979,135 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
         <v>46138.625</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>18</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" t="n">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>7</v>
+      </c>
+      <c r="R44" t="n">
         <v>5</v>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="n">
         <v>6</v>
       </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2</v>
-      </c>
-      <c r="S44" t="n">
-        <v>8</v>
-      </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
+        <v>20</v>
+      </c>
+      <c r="V44" t="n">
+        <v>11</v>
+      </c>
+      <c r="W44" t="n">
+        <v>14</v>
+      </c>
+      <c r="X44" t="n">
         <v>10</v>
       </c>
-      <c r="U44" t="n">
-        <v>12</v>
-      </c>
-      <c r="V44" t="n">
-        <v>12</v>
-      </c>
-      <c r="W44" t="n">
-        <v>11</v>
-      </c>
-      <c r="X44" t="n">
-        <v>14</v>
-      </c>
       <c r="Y44" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3.07</v>
+        <v>2.38</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO44" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AU44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV44" t="n">
         <v>0</v>
@@ -20116,31 +20116,31 @@
         <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY44" t="n">
         <v>1</v>
       </c>
       <c r="AZ44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA44" t="n">
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1475</v>
+        <v>-1</v>
       </c>
       <c r="BC44" t="n">
         <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="BE44" t="n">
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>3402</v>
+        <v>5013</v>
       </c>
       <c r="BG44" t="n">
         <v>2</v>
@@ -20152,35 +20152,35 @@
         <v>3</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BK44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BL44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM44" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS44" t="n">
         <v>3</v>
       </c>
-      <c r="BN44" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR44" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS44" t="n">
-        <v>0</v>
-      </c>
       <c r="BT44" t="n">
         <v>2</v>
       </c>
@@ -20188,25 +20188,25 @@
         <v>1</v>
       </c>
       <c r="BV44" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="BW44" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BX44" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="BY44" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="BZ44" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="CA44" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.59</v>
+        <v>3.44</v>
       </c>
       <c r="CC44" t="n">
         <v>0</v>
@@ -20254,76 +20254,76 @@
         <v>1</v>
       </c>
       <c r="CR44" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="CS44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CT44" t="n">
         <v>1</v>
       </c>
       <c r="CU44" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV44" t="n">
         <v>14</v>
       </c>
-      <c r="CV44" t="n">
+      <c r="CW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX44" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY44" t="n">
         <v>11</v>
       </c>
-      <c r="CW44" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX44" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY44" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ44" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DA44" t="n">
         <v>100</v>
       </c>
       <c r="DB44" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DC44" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.14</v>
+        <v>0.67</v>
       </c>
       <c r="DF44" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="DG44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="DH44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI44" t="n">
         <v>1.5</v>
       </c>
-      <c r="DI44" t="n">
-        <v>0.6</v>
-      </c>
       <c r="DJ44" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="DK44" t="n">
         <v>0</v>
       </c>
       <c r="DL44" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="DM44" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DN44" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20332,7 +20332,7 @@
         <v>1</v>
       </c>
       <c r="DR44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS44" t="b">
         <v>0</v>
@@ -20348,64 +20348,56 @@
       </c>
       <c r="DW44" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="DX44" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="DY44" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DZ44" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="EA44" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="DZ44" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="EA44" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="EB44" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="EC44" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="ED44" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EE44" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EF44" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EG44" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EH44" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EG44" t="inlineStr"/>
+      <c r="EH44" t="inlineStr"/>
       <c r="EI44" t="inlineStr"/>
       <c r="EJ44" t="inlineStr"/>
       <c r="EK44" t="inlineStr"/>
@@ -20427,46 +20419,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
         <v>46138.625</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>4</v>
@@ -20475,120 +20467,120 @@
         <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W45" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X45" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y45" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="Z45" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN45" t="n">
         <v>1.67</v>
       </c>
-      <c r="AJ45" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AO45" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AP45" t="n">
         <v>2.32</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1524</v>
+        <v>1475</v>
       </c>
       <c r="BC45" t="n">
         <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="BE45" t="n">
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1491</v>
+        <v>3402</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -20597,19 +20589,19 @@
         <v>1</v>
       </c>
       <c r="BI45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ45" t="n">
         <v>0</v>
       </c>
       <c r="BK45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BN45" t="n">
         <v>3</v>
@@ -20621,166 +20613,166 @@
         <v>0</v>
       </c>
       <c r="BQ45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS45" t="n">
         <v>0</v>
       </c>
       <c r="BT45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR45" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS45" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV45" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX45" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY45" t="n">
         <v>6</v>
       </c>
-      <c r="BU45" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV45" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>53</v>
-      </c>
-      <c r="BX45" t="n">
-        <v>68</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>92</v>
-      </c>
-      <c r="BZ45" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CA45" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="CB45" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI45" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ45" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ45" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS45" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT45" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU45" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV45" t="n">
-        <v>18</v>
-      </c>
-      <c r="CW45" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX45" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY45" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ45" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DA45" t="n">
         <v>100</v>
       </c>
       <c r="DB45" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="DC45" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="DF45" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH45" t="n">
         <v>1.5</v>
       </c>
-      <c r="DG45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH45" t="n">
-        <v>0.8</v>
-      </c>
       <c r="DI45" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="DJ45" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="DK45" t="n">
         <v>0</v>
       </c>
       <c r="DL45" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="DM45" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="DN45" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="DO45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
       </c>
       <c r="DQ45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS45" t="b">
         <v>0</v>
@@ -20792,52 +20784,68 @@
         <v>0</v>
       </c>
       <c r="DV45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW45" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DX45" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="DY45" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DZ45" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EA45" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB45" t="inlineStr">
         <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="EC45" t="inlineStr"/>
-      <c r="ED45" t="inlineStr"/>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="ED45" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
       <c r="EE45" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EF45" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EG45" t="inlineStr"/>
-      <c r="EH45" t="inlineStr"/>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EG45" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EH45" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
       <c r="EI45" t="inlineStr"/>
       <c r="EJ45" t="inlineStr"/>
       <c r="EK45" t="inlineStr"/>
@@ -20859,12 +20867,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
@@ -20874,19 +20882,19 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -20898,37 +20906,37 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" t="n">
         <v>7</v>
       </c>
-      <c r="R46" t="n">
-        <v>5</v>
-      </c>
-      <c r="S46" t="n">
-        <v>13</v>
-      </c>
-      <c r="T46" t="n">
-        <v>6</v>
-      </c>
-      <c r="U46" t="n">
-        <v>20</v>
-      </c>
-      <c r="V46" t="n">
-        <v>11</v>
-      </c>
       <c r="W46" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y46" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Z46" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
@@ -20936,79 +20944,79 @@
         <v>2</v>
       </c>
       <c r="AD46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AK46" t="n">
         <v>1.5</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AM46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AR46" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="AS46" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB46" t="n">
-        <v>-1</v>
+        <v>1524</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
@@ -21020,7 +21028,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>5013</v>
+        <v>1491</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -21029,124 +21037,124 @@
         <v>1</v>
       </c>
       <c r="BI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN46" t="n">
         <v>3</v>
       </c>
-      <c r="BJ46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN46" t="n">
-        <v>10</v>
-      </c>
       <c r="BO46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BU46" t="n">
         <v>1</v>
       </c>
       <c r="BV46" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="BW46" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
         <v>26</v>
       </c>
-      <c r="BX46" t="n">
-        <v>102</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CB46" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="CC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>16</v>
-      </c>
       <c r="CS46" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
         <v>9</v>
       </c>
-      <c r="CT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU46" t="n">
-        <v>10</v>
-      </c>
       <c r="CV46" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CW46" t="n">
         <v>1</v>
@@ -21155,7 +21163,7 @@
         <v>10</v>
       </c>
       <c r="CY46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CZ46" t="n">
         <v>50</v>
@@ -21164,28 +21172,28 @@
         <v>100</v>
       </c>
       <c r="DB46" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DC46" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF46" t="n">
-        <v>0.33</v>
+        <v>1.5</v>
       </c>
       <c r="DG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH46" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ46" t="n">
         <v>50</v>
@@ -21194,13 +21202,13 @@
         <v>0</v>
       </c>
       <c r="DL46" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="DO46" t="n">
         <v>11</v>
@@ -21209,7 +21217,7 @@
         <v>1</v>
       </c>
       <c r="DQ46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR46" t="b">
         <v>0</v>
@@ -21224,56 +21232,48 @@
         <v>0</v>
       </c>
       <c r="DV46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW46" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="DX46" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="ED46" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr"/>
+      <c r="ED46" t="inlineStr"/>
       <c r="EE46" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EG46" t="inlineStr"/>
@@ -21613,7 +21613,7 @@
         <v>2.13</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF47" t="n">
         <v>2.5</v>
@@ -21643,7 +21643,7 @@
         <v>3.46</v>
       </c>
       <c r="DO47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -25123,7 +25123,7 @@
         <v>2.79</v>
       </c>
       <c r="DO55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26443,7 +26443,7 @@
         <v>4.46</v>
       </c>
       <c r="DO58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28175,7 +28175,7 @@
         <v>2.89</v>
       </c>
       <c r="DO62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29055,7 +29055,7 @@
         <v>3.17</v>
       </c>
       <c r="DO64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29897,7 +29897,7 @@
         <v>1.8</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>2</v>
@@ -29927,7 +29927,7 @@
         <v>2.78</v>
       </c>
       <c r="DO66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31222,7 +31222,7 @@
         <v>54</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE69" t="n">
         <v>0.67</v>
@@ -31255,7 +31255,7 @@
         <v>2.73</v>
       </c>
       <c r="DO69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -35555,7 +35555,7 @@
         <v>2.69</v>
       </c>
       <c r="DO79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37295,7 +37295,7 @@
         <v>2.94</v>
       </c>
       <c r="DO83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37433,7 +37433,7 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
         <v>3</v>
@@ -37442,19 +37442,19 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W84" t="n">
         <v>16</v>
       </c>
       <c r="X84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y84" t="n">
         <v>41</v>
@@ -37612,13 +37612,13 @@
         <v>134</v>
       </c>
       <c r="BZ84" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CA84" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="CB84" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
@@ -37675,7 +37675,7 @@
         <v>1</v>
       </c>
       <c r="CU84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV84" t="n">
         <v>16</v>
@@ -37760,7 +37760,7 @@
       </c>
       <c r="DW84" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="DX84" t="inlineStr">
@@ -37770,42 +37770,42 @@
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC84" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED84" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr"/>
@@ -37831,76 +37831,76 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
         <v>46171.70833333334</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M85" t="n">
         <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R85" t="n">
         <v>4</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T85" t="n">
         <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V85" t="n">
         <v>11</v>
       </c>
       <c r="W85" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y85" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="Z85" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="inlineStr"/>
@@ -37908,157 +37908,157 @@
         <v>1</v>
       </c>
       <c r="AD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ85" t="n">
         <v>3</v>
       </c>
-      <c r="AE85" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AU85" t="n">
+      <c r="BA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>327</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>9465</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK85" t="n">
         <v>3</v>
       </c>
-      <c r="AV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>1471</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF85" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>1</v>
-      </c>
       <c r="BL85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BN85" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP85" t="n">
         <v>0</v>
       </c>
       <c r="BQ85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="BW85" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="BX85" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="BY85" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="CB85" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
@@ -38085,10 +38085,10 @@
         <v>1</v>
       </c>
       <c r="CK85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM85" t="n">
         <v>0</v>
@@ -38106,73 +38106,73 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CS85" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
       </c>
       <c r="CU85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV85" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CW85" t="n">
         <v>1</v>
       </c>
       <c r="CX85" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY85" t="n">
         <v>8</v>
       </c>
-      <c r="CY85" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ85" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="DA85" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DB85" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="DC85" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="DD85" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.14</v>
+        <v>0.67</v>
       </c>
       <c r="DF85" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DG85" t="n">
-        <v>0.17</v>
+        <v>0.8</v>
       </c>
       <c r="DH85" t="n">
         <v>1.1</v>
       </c>
       <c r="DI85" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="DJ85" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="DK85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="DO85" t="n">
         <v>11</v>
@@ -38187,7 +38187,7 @@
         <v>1</v>
       </c>
       <c r="DS85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT85" t="b">
         <v>0</v>
@@ -38198,46 +38198,34 @@
       <c r="DV85" t="b">
         <v>1</v>
       </c>
-      <c r="DW85" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="DX85" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="DY85" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
+      <c r="DW85" t="inlineStr"/>
+      <c r="DX85" t="inlineStr"/>
+      <c r="DY85" t="inlineStr"/>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr"/>
       <c r="ED85" t="inlineStr"/>
       <c r="EE85" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr"/>
@@ -38308,13 +38296,13 @@
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
       </c>
       <c r="T86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U86" t="n">
         <v>5</v>
@@ -38424,7 +38412,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>2011</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -38487,10 +38475,10 @@
         <v>0.59</v>
       </c>
       <c r="CA86" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="CB86" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="CC86" t="n">
         <v>0</v>
@@ -38632,42 +38620,42 @@
       </c>
       <c r="DW86" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="DX86" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="ED86" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE86" t="inlineStr"/>
@@ -38676,12 +38664,12 @@
       <c r="EH86" t="inlineStr"/>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK86" t="inlineStr"/>
@@ -38754,13 +38742,13 @@
         <v>6</v>
       </c>
       <c r="T87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U87" t="n">
         <v>10</v>
       </c>
       <c r="V87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W87" t="n">
         <v>6</v>
@@ -38864,7 +38852,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>15420</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -38927,10 +38915,10 @@
         <v>1.63</v>
       </c>
       <c r="CA87" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="CB87" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="CC87" t="n">
         <v>0</v>
@@ -38978,19 +38966,19 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CS87" t="n">
         <v>29</v>
       </c>
       <c r="CT87" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU87" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CV87" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CW87" t="n">
         <v>1</v>
@@ -39082,22 +39070,22 @@
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EC87" t="inlineStr"/>
@@ -39288,7 +39276,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>5611</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>
@@ -39496,32 +39484,32 @@
       </c>
       <c r="DW88" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="DX88" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr"/>
@@ -39551,76 +39539,76 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F89" s="1" t="n">
         <v>46171.70833333334</v>
       </c>
       <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
         <v>3</v>
       </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>5</v>
+      </c>
+      <c r="R89" t="n">
         <v>4</v>
-      </c>
-      <c r="J89" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" t="n">
-        <v>6</v>
-      </c>
-      <c r="L89" t="n">
-        <v>11</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>9</v>
-      </c>
-      <c r="R89" t="n">
-        <v>5</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
       </c>
       <c r="T89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U89" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V89" t="n">
+        <v>11</v>
+      </c>
+      <c r="W89" t="n">
+        <v>15</v>
+      </c>
+      <c r="X89" t="n">
         <v>10</v>
       </c>
-      <c r="W89" t="n">
-        <v>12</v>
-      </c>
-      <c r="X89" t="n">
-        <v>7</v>
-      </c>
       <c r="Y89" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z89" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="AA89" t="inlineStr"/>
       <c r="AB89" t="inlineStr"/>
@@ -39628,158 +39616,158 @@
         <v>1</v>
       </c>
       <c r="AD89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AF89" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="AG89" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AJ89" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AL89" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AM89" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>1471</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>8273</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA89" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN89" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO89" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AP89" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AQ89" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR89" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ89" t="n">
+      <c r="CB89" t="n">
         <v>3</v>
       </c>
-      <c r="BA89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>327</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG89" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI89" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK89" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL89" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM89" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN89" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV89" t="n">
-        <v>54</v>
-      </c>
-      <c r="BW89" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX89" t="n">
-        <v>111</v>
-      </c>
-      <c r="BY89" t="n">
-        <v>97</v>
-      </c>
-      <c r="BZ89" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CA89" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB89" t="n">
-        <v>3.53</v>
-      </c>
       <c r="CC89" t="n">
         <v>0</v>
       </c>
@@ -39805,10 +39793,10 @@
         <v>1</v>
       </c>
       <c r="CK89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM89" t="n">
         <v>0</v>
@@ -39826,73 +39814,73 @@
         <v>1</v>
       </c>
       <c r="CR89" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CS89" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT89" t="n">
         <v>1</v>
       </c>
       <c r="CU89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CV89" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CW89" t="n">
         <v>1</v>
       </c>
       <c r="CX89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY89" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ89" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="DA89" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="DB89" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="DC89" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="DF89" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="DG89" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="DH89" t="n">
         <v>1.1</v>
       </c>
       <c r="DI89" t="n">
-        <v>1.1</v>
+        <v>0.64</v>
       </c>
       <c r="DJ89" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="DK89" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL89" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="DM89" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DN89" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="DO89" t="n">
         <v>11</v>
@@ -39907,7 +39895,7 @@
         <v>1</v>
       </c>
       <c r="DS89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT89" t="b">
         <v>0</v>
@@ -39918,42 +39906,502 @@
       <c r="DV89" t="b">
         <v>1</v>
       </c>
-      <c r="DW89" t="inlineStr"/>
-      <c r="DX89" t="inlineStr"/>
-      <c r="DY89" t="inlineStr"/>
+      <c r="DW89" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="DX89" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
       <c r="DZ89" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EA89" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB89" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EC89" t="inlineStr"/>
       <c r="ED89" t="inlineStr"/>
       <c r="EE89" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EF89" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EG89" t="inlineStr"/>
-      <c r="EH89" t="inlineStr"/>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EG89" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
       <c r="EI89" t="inlineStr"/>
       <c r="EJ89" t="inlineStr"/>
       <c r="EK89" t="inlineStr"/>
       <c r="EL89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Norway_Eliteserien_2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>46172.58333333334</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" t="n">
+        <v>10</v>
+      </c>
+      <c r="L90" t="n">
+        <v>16</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>5</v>
+      </c>
+      <c r="R90" t="n">
+        <v>4</v>
+      </c>
+      <c r="S90" t="n">
+        <v>9</v>
+      </c>
+      <c r="T90" t="n">
+        <v>12</v>
+      </c>
+      <c r="U90" t="n">
+        <v>14</v>
+      </c>
+      <c r="V90" t="n">
+        <v>16</v>
+      </c>
+      <c r="W90" t="n">
+        <v>13</v>
+      </c>
+      <c r="X90" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>333</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>5112</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY90" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL90" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM90" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN90" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO90" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW90" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="DX90" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED90" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EE90" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EF90" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EG90" t="inlineStr"/>
+      <c r="EH90" t="inlineStr"/>
+      <c r="EI90" t="inlineStr"/>
+      <c r="EJ90" t="inlineStr"/>
+      <c r="EK90" t="inlineStr"/>
+      <c r="EL90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
